--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260904.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>245,070,790</t>
+          <t>2,361,431</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,361,431</t>
+          <t>245,070,790</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>22,428,993</t>
+          <t>10,897,809</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>10,897,809</t>
+          <t>22,428,993</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
